--- a/business_forms/045_receiving_management_survey--business_forms.xlsx
+++ b/business_forms/045_receiving_management_survey--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,63 +515,63 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_1</t>
+          <t>general_management_practices_page_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Receiving Management Survey</t>
+          <t>General Management Practices</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_2</t>
+          <t>general_management_practices_page_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Receiving Management Survey</t>
+          <t>What are the current management procedures used?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_3</t>
+          <t>general_management_practices_page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Receiving Management Survey</t>
+          <t>What are the management goals and objectives for the next quarter?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,23 +584,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_4</t>
+          <t>receiving_page_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Receiving Management Survey</t>
+          <t>How often is receiving done at the department/section?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_5</t>
+          <t>receiving_page_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Receiving Management Survey</t>
+          <t>Are there any specific actions taken during receiving?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,23 +630,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_6</t>
+          <t>receiving_page_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Receiving Management Survey</t>
+          <t>Are there any issues that have arisen during receiving?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_7</t>
+          <t>receiving_page_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Receiving Management Survey</t>
+          <t>Can you provide more information about receiving management?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_8</t>
+          <t>receiving_page_5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Receiving Management Survey</t>
+          <t>What are your suggestions for improvement?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,69 +699,69 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_9</t>
+          <t>date_page_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Receiving Management Survey</t>
+          <t>What date is the last time receiving was done?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_10</t>
+          <t>time_page_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Receiving Management Survey</t>
+          <t>What time is receiving usually done?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_11</t>
+          <t>receiving_page_6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Receiving Management Survey</t>
+          <t>What is the average number of items received?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,35 +773,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_12</t>
+          <t>receiving_page_7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Receiving Management Survey</t>
+          <t>What is the average weight of items received?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_13</t>
+          <t>receiving_page_8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Receiving Management Survey</t>
+          <t>Are there any specific receiving locations?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,16 +819,108 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_14</t>
+          <t>receiving_page_9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Receiving Management Survey</t>
+          <t>What is the average time spent on receiving?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>receiving_page_10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>What is the average number of items received per week?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>receiving_page_11</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>What time of day is receiving usually done?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>receiving_page_12</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>What type of receiving is usually done?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>receiving_page_13</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Additional comments</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -845,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -873,187 +965,255 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_3_choices</t>
+          <t>receiving_page_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_3_choices</t>
+          <t>receiving_page_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_4_choices</t>
+          <t>receiving_page_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_4_choices</t>
+          <t>receiving_page_3_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_10_choices</t>
+          <t>receiving_page_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_10_choices</t>
+          <t>receiving_page_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other_(please_describe)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other (please describe)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_10_choices</t>
+          <t>receiving_page_8_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_11_choices</t>
+          <t>receiving_page_8_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_11_choices</t>
+          <t>receiving_page_8_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other_(please_describe)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other (please describe)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_11_choices</t>
+          <t>receiving_page_11_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>receiving_management_survey_page_11_choices</t>
+          <t>receiving_page_11_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Afternoon</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>receiving_page_11_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>evening</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>receiving_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>receiving_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>virtual</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>receiving_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>other_(please_describe)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Other (please describe)</t>
         </is>
       </c>
     </row>
